--- a/novo projeto/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-26).xlsx
+++ b/novo projeto/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-26).xlsx
@@ -912,69 +912,69 @@
   </si>
   <si>
     <t>214
-167</t>
-  </si>
-  <si>
-    <t>34</t>
-  </si>
-  <si>
-    <t>R$ 1.700.173,24</t>
-  </si>
-  <si>
-    <t>R$ 9.551,54
-R$ 9.715,49</t>
-  </si>
-  <si>
-    <t>(3.8%)
-(2.8%)</t>
+170</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>R$ 1.737.341,01</t>
+  </si>
+  <si>
+    <t>R$ 9.545,83
+R$ 9.740,67</t>
+  </si>
+  <si>
+    <t>(4.3%)
+(2.9%)</t>
   </si>
   <si>
     <t>98.3</t>
   </si>
   <si>
-    <t>(8.6%)</t>
-  </si>
-  <si>
-    <t>45.3%</t>
-  </si>
-  <si>
-    <t>0.2%</t>
+    <t>(8.9%)</t>
+  </si>
+  <si>
+    <t>45.8%</t>
+  </si>
+  <si>
+    <t>0.9%</t>
   </si>
   <si>
     <t>2.6%</t>
   </si>
   <si>
-    <t>0.5%</t>
-  </si>
-  <si>
-    <t>28.7</t>
-  </si>
-  <si>
-    <t>64.8%</t>
-  </si>
-  <si>
-    <t>13.7%</t>
+    <t>0.6%</t>
+  </si>
+  <si>
+    <t>29.0</t>
+  </si>
+  <si>
+    <t>64.6%</t>
+  </si>
+  <si>
+    <t>14.3%</t>
   </si>
   <si>
     <t>6.7</t>
   </si>
   <si>
-    <t>7.0</t>
-  </si>
-  <si>
-    <t>13.3</t>
-  </si>
-  <si>
-    <t>20.5</t>
-  </si>
-  <si>
-    <t>65.9%</t>
-  </si>
-  <si>
-    <t>-R$ 46.263,53</t>
-  </si>
-  <si>
-    <t>2.95</t>
+    <t>7.2</t>
+  </si>
+  <si>
+    <t>13.9</t>
+  </si>
+  <si>
+    <t>20.8</t>
+  </si>
+  <si>
+    <t>65.1%</t>
+  </si>
+  <si>
+    <t>-R$ 50.719,26</t>
+  </si>
+  <si>
+    <t>2.94</t>
   </si>
   <si>
     <t>3.52</t>
@@ -1884,7 +1884,9 @@
       <c r="AB4" s="8">
         <v>4.5</v>
       </c>
-      <c r="AC4" s="8"/>
+      <c r="AC4" s="8">
+        <v>11.523903000000001</v>
+      </c>
       <c r="AD4" s="8">
         <v>16.763157894736842</v>
       </c>
@@ -2630,7 +2632,9 @@
       <c r="AB10" s="8">
         <v>1.8843920634920635</v>
       </c>
-      <c r="AC10" s="8"/>
+      <c r="AC10" s="8">
+        <v>8.3037030000000005</v>
+      </c>
       <c r="AD10" s="8">
         <v>15.253439682539682</v>
       </c>
@@ -4382,7 +4386,7 @@
         <v>19536</v>
       </c>
       <c r="B24" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C24" s="4">
         <v>44</v>
@@ -4418,25 +4422,59 @@
       <c t="s" r="N24" s="4">
         <v>52</v>
       </c>
-      <c r="O24" s="5"/>
-      <c r="P24" s="5"/>
-      <c r="Q24" s="6"/>
-      <c r="R24" s="7"/>
-      <c r="S24" s="6"/>
-      <c r="T24" s="6"/>
-      <c r="U24" s="6"/>
-      <c r="V24" s="6"/>
-      <c r="W24" s="6"/>
-      <c r="X24" s="8"/>
-      <c r="Y24" s="6"/>
-      <c r="Z24" s="6"/>
-      <c r="AA24" s="8"/>
-      <c r="AB24" s="8"/>
+      <c r="O24" s="5">
+        <v>11175.92</v>
+      </c>
+      <c r="P24" s="5">
+        <v>11175.92</v>
+      </c>
+      <c r="Q24" s="6">
+        <v>0.0037884843727264972</v>
+      </c>
+      <c r="R24" s="7">
+        <v>125</v>
+      </c>
+      <c r="S24" s="6">
+        <v>0.0080645161290322509</v>
+      </c>
+      <c r="T24" s="6">
+        <v>-0.00072656210853334663</v>
+      </c>
+      <c r="U24" s="6">
+        <v>-0.32657177216730254</v>
+      </c>
+      <c r="V24" s="6">
+        <v>0.013464126443281627</v>
+      </c>
+      <c r="W24" s="6">
+        <v>-0.0034991302729439726</v>
+      </c>
+      <c r="X24" s="8">
+        <v>34.328471874999998</v>
+      </c>
+      <c r="Y24" s="6">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="Z24" s="6">
+        <v>0.25</v>
+      </c>
+      <c r="AA24" s="8">
+        <v>7.7436636363636362</v>
+      </c>
+      <c r="AB24" s="8">
+        <v>10.771701041666667</v>
+      </c>
       <c r="AC24" s="8"/>
-      <c r="AD24" s="8"/>
-      <c r="AE24" s="6"/>
+      <c r="AD24" s="8">
+        <v>25.497569791666667</v>
+      </c>
+      <c r="AE24" s="6">
+        <v>0.39583333333333331</v>
+      </c>
       <c r="AF24" s="9"/>
-      <c r="AG24" s="5"/>
+      <c r="AG24" s="5">
+        <v>-538.34000000000003</v>
+      </c>
       <c r="AH24" s="10">
         <v>2</v>
       </c>
@@ -4948,7 +4986,9 @@
       <c r="AB28" s="8">
         <v>9.2279999999999998</v>
       </c>
-      <c r="AC28" s="8"/>
+      <c r="AC28" s="8">
+        <v>11.186332999999999</v>
+      </c>
       <c r="AD28" s="8">
         <v>18.136333999999998</v>
       </c>
@@ -5077,7 +5117,9 @@
       <c r="AB29" s="8">
         <v>12.251551162790697</v>
       </c>
-      <c r="AC29" s="8"/>
+      <c r="AC29" s="8">
+        <v>23.962057000000001</v>
+      </c>
       <c r="AD29" s="8">
         <v>31.376136363636363</v>
       </c>
@@ -5202,7 +5244,9 @@
       <c r="AB30" s="8">
         <v>2.5038899999999997</v>
       </c>
-      <c r="AC30" s="8"/>
+      <c r="AC30" s="8">
+        <v>5.5999990000000004</v>
+      </c>
       <c r="AD30" s="8">
         <v>12.567223333333335</v>
       </c>
@@ -5593,7 +5637,9 @@
       <c r="AB33" s="8">
         <v>7.3997017857142859</v>
       </c>
-      <c r="AC33" s="8"/>
+      <c r="AC33" s="8">
+        <v>9.3735110000000006</v>
+      </c>
       <c r="AD33" s="8">
         <v>16.330058928571429</v>
       </c>
@@ -5696,10 +5742,10 @@
         <v>-0.027472527472527486</v>
       </c>
       <c r="T34" s="6">
-        <v>0.0008885564472617169</v>
+        <v>0.071485535635879421</v>
       </c>
       <c r="U34" s="6">
-        <v>-0.33966026799898485</v>
+        <v>-0.26906328881036712</v>
       </c>
       <c r="V34" s="6">
         <v>0.054479872022296927</v>
@@ -6345,7 +6391,9 @@
       <c r="AB39" s="8">
         <v>6.8946666666666667</v>
       </c>
-      <c r="AC39" s="8"/>
+      <c r="AC39" s="8">
+        <v>10.537958</v>
+      </c>
       <c r="AD39" s="8">
         <v>17.718929629629631</v>
       </c>
@@ -6448,10 +6496,10 @@
         <v>0.084415584415584499</v>
       </c>
       <c r="T40" s="6">
-        <v>0.34495409822220346</v>
+        <v>0.33891702208521601</v>
       </c>
       <c r="U40" s="6">
-        <v>0.035164815675013721</v>
+        <v>0.029127739538026269</v>
       </c>
       <c r="V40" s="6">
         <v>0.024559745506242698</v>
@@ -7093,7 +7141,9 @@
       <c r="AB45" s="8">
         <v>4.9459770114942527</v>
       </c>
-      <c r="AC45" s="8"/>
+      <c r="AC45" s="8">
+        <v>8.3404209999999992</v>
+      </c>
       <c r="AD45" s="8">
         <v>14.42191011235955</v>
       </c>
@@ -7738,7 +7788,9 @@
       <c r="AB50" s="8">
         <v>10.370164197530864</v>
       </c>
-      <c r="AC50" s="8"/>
+      <c r="AC50" s="8">
+        <v>13.968517</v>
+      </c>
       <c r="AD50" s="8">
         <v>21.914814814814815</v>
       </c>
@@ -8091,7 +8143,9 @@
       <c r="AB53" s="8">
         <v>4.6651522727272727</v>
       </c>
-      <c r="AC53" s="8"/>
+      <c r="AC53" s="8">
+        <v>8.3893930000000001</v>
+      </c>
       <c r="AD53" s="8">
         <v>15.330302272727273</v>
       </c>
@@ -8220,7 +8274,9 @@
       <c r="AB54" s="8">
         <v>13.025</v>
       </c>
-      <c r="AC54" s="8"/>
+      <c r="AC54" s="8">
+        <v>20.247057999999999</v>
+      </c>
       <c r="AD54" s="8">
         <v>27.165195588235296</v>
       </c>
@@ -8349,7 +8405,9 @@
       <c r="AB55" s="8">
         <v>17.132375862068965</v>
       </c>
-      <c r="AC55" s="8"/>
+      <c r="AC55" s="8">
+        <v>21.328396999999999</v>
+      </c>
       <c r="AD55" s="8">
         <v>28.218965517241383</v>
       </c>
@@ -9000,7 +9058,9 @@
       <c r="AB60" s="8">
         <v>3.1764948717948718</v>
       </c>
-      <c r="AC60" s="8"/>
+      <c r="AC60" s="8">
+        <v>5.8161839999999998</v>
+      </c>
       <c r="AD60" s="8">
         <v>13.310163414634145</v>
       </c>
@@ -9309,7 +9369,7 @@
         <v>19632</v>
       </c>
       <c r="B63" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C63" s="4">
         <v>44</v>
@@ -9345,11 +9405,21 @@
       <c t="s" r="N63" s="4">
         <v>52</v>
       </c>
-      <c r="O63" s="5"/>
-      <c r="P63" s="5"/>
-      <c r="Q63" s="6"/>
-      <c r="R63" s="7"/>
-      <c r="S63" s="6"/>
+      <c r="O63" s="5">
+        <v>0</v>
+      </c>
+      <c r="P63" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="6">
+        <v>-1</v>
+      </c>
+      <c r="R63" s="7">
+        <v>0</v>
+      </c>
+      <c r="S63" s="6">
+        <v>-1</v>
+      </c>
       <c r="T63" s="6"/>
       <c r="U63" s="6"/>
       <c r="V63" s="6"/>
@@ -9363,7 +9433,9 @@
       <c r="AD63" s="8"/>
       <c r="AE63" s="6"/>
       <c r="AF63" s="9"/>
-      <c r="AG63" s="5"/>
+      <c r="AG63" s="5">
+        <v>0</v>
+      </c>
       <c r="AH63" s="10">
         <v>3</v>
       </c>
@@ -10353,7 +10425,9 @@
       <c r="AB71" s="8">
         <v>7.1271106666666677</v>
       </c>
-      <c r="AC71" s="8"/>
+      <c r="AC71" s="8">
+        <v>11.477111000000001</v>
+      </c>
       <c r="AD71" s="8">
         <v>19.079653246753246</v>
       </c>
@@ -10831,7 +10905,9 @@
       <c r="AB75" s="8">
         <v>6.3170948717948718</v>
       </c>
-      <c r="AC75" s="8"/>
+      <c r="AC75" s="8">
+        <v>12.686752</v>
+      </c>
       <c r="AD75" s="8">
         <v>19.629058974358976</v>
       </c>
@@ -10882,7 +10958,7 @@
         <v>19661</v>
       </c>
       <c r="B76" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C76" s="4">
         <v>44</v>
@@ -10916,25 +10992,61 @@
       <c t="s" r="N76" s="4">
         <v>52</v>
       </c>
-      <c r="O76" s="5"/>
-      <c r="P76" s="5"/>
-      <c r="Q76" s="6"/>
-      <c r="R76" s="7"/>
-      <c r="S76" s="6"/>
-      <c r="T76" s="6"/>
-      <c r="U76" s="6"/>
-      <c r="V76" s="6"/>
-      <c r="W76" s="6"/>
-      <c r="X76" s="8"/>
-      <c r="Y76" s="6"/>
-      <c r="Z76" s="6"/>
-      <c r="AA76" s="8"/>
-      <c r="AB76" s="8"/>
-      <c r="AC76" s="8"/>
-      <c r="AD76" s="8"/>
-      <c r="AE76" s="6"/>
+      <c r="O76" s="5">
+        <v>11076.360000000001</v>
+      </c>
+      <c r="P76" s="5">
+        <v>11076.360000000001</v>
+      </c>
+      <c r="Q76" s="6">
+        <v>0.088510864117456345</v>
+      </c>
+      <c r="R76" s="7">
+        <v>123</v>
+      </c>
+      <c r="S76" s="6">
+        <v>0.060344827586206851</v>
+      </c>
+      <c r="T76" s="6">
+        <v>0.056000111950135233</v>
+      </c>
+      <c r="U76" s="6">
+        <v>-0.32406337461043155</v>
+      </c>
+      <c r="V76" s="6">
+        <v>0.076334599092120509</v>
+      </c>
+      <c r="W76" s="6">
+        <v>0.060579423204012869</v>
+      </c>
+      <c r="X76" s="8">
+        <v>54.98564861111111</v>
+      </c>
+      <c r="Y76" s="6">
+        <v>0.19444444444444445</v>
+      </c>
+      <c r="Z76" s="6">
+        <v>0.73611111111111116</v>
+      </c>
+      <c r="AA76" s="8">
+        <v>6.5527559055118116</v>
+      </c>
+      <c r="AB76" s="8">
+        <v>26.282176388888889</v>
+      </c>
+      <c r="AC76" s="8">
+        <v>32.729323999999998</v>
+      </c>
+      <c r="AD76" s="8">
+        <v>41.696065277777777</v>
+      </c>
+      <c r="AE76" s="6">
+        <v>0.1111111111111111</v>
+      </c>
       <c r="AF76" s="9"/>
-      <c r="AG76" s="5"/>
+      <c r="AG76" s="5">
+        <v>-176.80000000000001</v>
+      </c>
       <c r="AH76" s="10">
         <v>2</v>
       </c>
@@ -12464,7 +12576,7 @@
         <v>0</v>
       </c>
       <c r="AH88" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI88" s="11"/>
       <c r="AJ88" s="13">
@@ -12503,7 +12615,7 @@
         <v>19693</v>
       </c>
       <c r="B89" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C89" s="4">
         <v>44</v>
@@ -12537,25 +12649,59 @@
       <c t="s" r="N89" s="4">
         <v>52</v>
       </c>
-      <c r="O89" s="5"/>
-      <c r="P89" s="5"/>
-      <c r="Q89" s="6"/>
-      <c r="R89" s="7"/>
-      <c r="S89" s="6"/>
-      <c r="T89" s="6"/>
-      <c r="U89" s="6"/>
-      <c r="V89" s="6"/>
-      <c r="W89" s="6"/>
-      <c r="X89" s="8"/>
-      <c r="Y89" s="6"/>
-      <c r="Z89" s="6"/>
-      <c r="AA89" s="8"/>
-      <c r="AB89" s="8"/>
+      <c r="O89" s="5">
+        <v>11174.9</v>
+      </c>
+      <c r="P89" s="5">
+        <v>11174.9</v>
+      </c>
+      <c r="Q89" s="6">
+        <v>-0.23603643267181817</v>
+      </c>
+      <c r="R89" s="7">
+        <v>102</v>
+      </c>
+      <c r="S89" s="6">
+        <v>-0.22727272727272729</v>
+      </c>
+      <c r="T89" s="6">
+        <v>0.78436998093942678</v>
+      </c>
+      <c r="U89" s="6">
+        <v>0.45788831219966175</v>
+      </c>
+      <c r="V89" s="6">
+        <v>0.023097119437310402</v>
+      </c>
+      <c r="W89" s="6">
+        <v>0.010808866298579854</v>
+      </c>
+      <c r="X89" s="8">
+        <v>43.499019607843131</v>
+      </c>
+      <c r="Y89" s="6">
+        <v>0.84313725490196079</v>
+      </c>
+      <c r="Z89" s="6">
+        <v>0.56862745098039214</v>
+      </c>
+      <c r="AA89" s="8">
+        <v>13.918300980392157</v>
+      </c>
+      <c r="AB89" s="8">
+        <v>11.387907843137256</v>
+      </c>
       <c r="AC89" s="8"/>
-      <c r="AD89" s="8"/>
-      <c r="AE89" s="6"/>
+      <c r="AD89" s="8">
+        <v>34.191176470588232</v>
+      </c>
+      <c r="AE89" s="6">
+        <v>0.078431372549019607</v>
+      </c>
       <c r="AF89" s="9"/>
-      <c r="AG89" s="5"/>
+      <c r="AG89" s="5">
+        <v>0</v>
+      </c>
       <c r="AH89" s="10">
         <v>2</v>
       </c>
@@ -12674,7 +12820,9 @@
       <c r="AB90" s="8">
         <v>13.336616666666666</v>
       </c>
-      <c r="AC90" s="8"/>
+      <c r="AC90" s="8">
+        <v>46.183802</v>
+      </c>
       <c r="AD90" s="8">
         <v>49.967777333333331</v>
       </c>
@@ -15039,7 +15187,9 @@
       <c r="AB109" s="8">
         <v>15.977631578947367</v>
       </c>
-      <c r="AC109" s="8"/>
+      <c r="AC109" s="8">
+        <v>21.759682000000002</v>
+      </c>
       <c r="AD109" s="8">
         <v>29.77061315789474</v>
       </c>
@@ -16481,7 +16631,7 @@
         <v>0</v>
       </c>
       <c r="AH121" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI121" s="11"/>
       <c r="AJ121" s="13">
@@ -17112,7 +17262,9 @@
       <c r="AB126" s="8">
         <v>7.9961099999999998</v>
       </c>
-      <c r="AC126" s="8"/>
+      <c r="AC126" s="8">
+        <v>11.980454</v>
+      </c>
       <c r="AD126" s="8">
         <v>18.972223333333332</v>
       </c>
@@ -18428,7 +18580,7 @@
         <v>-556.25</v>
       </c>
       <c r="AH136" s="10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AI136" s="11"/>
       <c r="AJ136" s="13">
@@ -19882,10 +20034,10 @@
         <v>-0.25</v>
       </c>
       <c r="T148" s="6">
-        <v>0</v>
+        <v>1.4307893305266146</v>
       </c>
       <c r="U148" s="6">
-        <v>-0.29218159312826941</v>
+        <v>1.1386077373983452</v>
       </c>
       <c r="V148" s="6">
         <v>0.02409530623588264</v>
@@ -20529,7 +20681,9 @@
       <c r="AB153" s="8">
         <v>8.9364337209302338</v>
       </c>
-      <c r="AC153" s="8"/>
+      <c r="AC153" s="8">
+        <v>15.045508</v>
+      </c>
       <c r="AD153" s="8">
         <v>21.982777777777777</v>
       </c>
@@ -20668,7 +20822,7 @@
         <v>388.19999999999999</v>
       </c>
       <c r="AH154" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI154" s="11"/>
       <c r="AJ154" s="13">
@@ -21618,7 +21772,9 @@
       <c r="AB162" s="8">
         <v>4.1686999999999994</v>
       </c>
-      <c r="AC162" s="8"/>
+      <c r="AC162" s="8">
+        <v>13.888617</v>
+      </c>
       <c r="AD162" s="8">
         <v>21.824390243902439</v>
       </c>
@@ -22104,7 +22260,9 @@
       <c r="AB166" s="8">
         <v>21.958640740740741</v>
       </c>
-      <c r="AC166" s="8"/>
+      <c r="AC166" s="8">
+        <v>26.693698000000001</v>
+      </c>
       <c r="AD166" s="8">
         <v>33.739507407407409</v>
       </c>
@@ -23019,7 +23177,9 @@
       <c r="AB173" s="8">
         <v>11.20673829787234</v>
       </c>
-      <c r="AC173" s="8"/>
+      <c r="AC173" s="8">
+        <v>17.945827000000001</v>
+      </c>
       <c r="AD173" s="8">
         <v>23.061727777777779</v>
       </c>
@@ -24321,7 +24481,9 @@
       <c r="AB183" s="8">
         <v>3.7958339285714287</v>
       </c>
-      <c r="AC183" s="8"/>
+      <c r="AC183" s="8">
+        <v>8.3749990000000007</v>
+      </c>
       <c r="AD183" s="8">
         <v>15.616666666666667</v>
       </c>
@@ -24805,7 +24967,9 @@
       <c r="AB187" s="8">
         <v>6.2127470588235294</v>
       </c>
-      <c r="AC187" s="8"/>
+      <c r="AC187" s="8">
+        <v>13.839214999999999</v>
+      </c>
       <c r="AD187" s="8">
         <v>20.812747058823533</v>
       </c>
@@ -25067,7 +25231,9 @@
       <c r="AB189" s="8">
         <v>12.976271186440679</v>
       </c>
-      <c r="AC189" s="8"/>
+      <c r="AC189" s="8">
+        <v>16.813098</v>
+      </c>
       <c r="AD189" s="8">
         <v>23.546111666666665</v>
       </c>
@@ -25196,7 +25362,9 @@
       <c r="AB190" s="8">
         <v>3.9844096774193547</v>
       </c>
-      <c r="AC190" s="8"/>
+      <c r="AC190" s="8">
+        <v>8.7505369999999996</v>
+      </c>
       <c r="AD190" s="8">
         <v>15.713441935483869</v>
       </c>
@@ -25976,7 +26144,9 @@
       <c r="AB196" s="8">
         <v>16.039390909090908</v>
       </c>
-      <c r="AC196" s="8"/>
+      <c r="AC196" s="8">
+        <v>33.332447999999999</v>
+      </c>
       <c r="AD196" s="8">
         <v>41.2303</v>
       </c>
@@ -26367,7 +26537,9 @@
       <c r="AB199" s="8">
         <v>29.639189189189192</v>
       </c>
-      <c r="AC199" s="8"/>
+      <c r="AC199" s="8">
+        <v>72.861118000000005</v>
+      </c>
       <c r="AD199" s="8">
         <v>80.106305405405408</v>
       </c>
@@ -26496,7 +26668,9 @@
       <c r="AB200" s="8">
         <v>3.6297642857142853</v>
       </c>
-      <c r="AC200" s="8"/>
+      <c r="AC200" s="8">
+        <v>9.6730940000000007</v>
+      </c>
       <c r="AD200" s="8">
         <v>16.539285714285715</v>
       </c>
@@ -27069,7 +27243,9 @@
       <c r="AB205" s="8">
         <v>2.7760000000000002</v>
       </c>
-      <c r="AC205" s="8"/>
+      <c r="AC205" s="8">
+        <v>8.6348880000000001</v>
+      </c>
       <c r="AD205" s="8">
         <v>14.766048148148148</v>
       </c>
@@ -27247,7 +27423,7 @@
         <v>19962</v>
       </c>
       <c r="B207" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C207" s="4">
         <v>44</v>
@@ -27283,25 +27459,57 @@
       <c t="s" r="N207" s="4">
         <v>52</v>
       </c>
-      <c r="O207" s="5"/>
-      <c r="P207" s="5"/>
+      <c r="O207" s="5">
+        <v>3740.5900000000001</v>
+      </c>
+      <c r="P207" s="5">
+        <v>3740.5900000000001</v>
+      </c>
       <c r="Q207" s="6"/>
-      <c r="R207" s="7"/>
+      <c r="R207" s="7">
+        <v>40</v>
+      </c>
       <c r="S207" s="6"/>
-      <c r="T207" s="6"/>
-      <c r="U207" s="6"/>
-      <c r="V207" s="6"/>
-      <c r="W207" s="6"/>
-      <c r="X207" s="8"/>
-      <c r="Y207" s="6"/>
-      <c r="Z207" s="6"/>
-      <c r="AA207" s="8"/>
-      <c r="AB207" s="8"/>
-      <c r="AC207" s="8"/>
-      <c r="AD207" s="8"/>
-      <c r="AE207" s="6"/>
+      <c r="T207" s="6">
+        <v>0.0030259932256676086</v>
+      </c>
+      <c r="U207" s="6">
+        <v>-0.31803833085155014</v>
+      </c>
+      <c r="V207" s="6">
+        <v>0.10249519460833718</v>
+      </c>
+      <c r="W207" s="6">
+        <v>0.062055050139149172</v>
+      </c>
+      <c r="X207" s="8">
+        <v>28.031578947368423</v>
+      </c>
+      <c r="Y207" s="6">
+        <v>0.89473684210526316</v>
+      </c>
+      <c r="Z207" s="6">
+        <v>0.052631578947368418</v>
+      </c>
+      <c r="AA207" s="8">
+        <v>7.4258763157894734</v>
+      </c>
+      <c r="AB207" s="8">
+        <v>7.4447368421052627</v>
+      </c>
+      <c r="AC207" s="8">
+        <v>14.357236</v>
+      </c>
+      <c r="AD207" s="8">
+        <v>21.077194736842106</v>
+      </c>
+      <c r="AE207" s="6">
+        <v>0.78947368421052633</v>
+      </c>
       <c r="AF207" s="9"/>
-      <c r="AG207" s="5"/>
+      <c r="AG207" s="5">
+        <v>-3740.5900000000001</v>
+      </c>
       <c r="AH207" s="10">
         <v>4</v>
       </c>
